--- a/ozon_products_data.xlsx
+++ b/ozon_products_data.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>333 ₽</t>
+          <t>376 ₽</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -473,12 +473,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Шапка с помпоном Aldini Зимняя коллекция</t>
+          <t>Шапка бини мужская зимняя</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>549 ₽</t>
+          <t>375 ₽</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -493,12 +493,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Шапка бини woolcraft NEW Осень - Зима 2025 Бини</t>
+          <t>Шапка бини Vorozhtsov Шапки</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>222 ₽</t>
+          <t>642 ₽</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -513,12 +513,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Шапка комплект с аксессуаром</t>
+          <t>Шапка karoca Теплые шапки для мужчин</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>459 ₽</t>
+          <t>477 ₽</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -538,7 +538,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>428 ₽</t>
+          <t>473 ₽</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -553,12 +553,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Шапка karoca Теплые шапки для мужчин</t>
+          <t>Шапка бини Aldini Зимняя коллекция</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>550 ₽</t>
+          <t>535 ₽</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -573,12 +573,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Шапка черная зимняя мужская</t>
+          <t>Балаклава шлем MotoLike</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>197 ₽</t>
+          <t>631 ₽</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -593,12 +593,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Шапка бини FashionVerse</t>
+          <t>Шапка бини WloO! шапки и снуды</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>525 ₽</t>
+          <t>1 012 ₽</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -613,12 +613,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Шапка MARSTON мужская теплая</t>
+          <t>Шапка черная зимняя мужская</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>550 ₽</t>
+          <t>179 ₽</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1 127 ₽</t>
+          <t>1 308 ₽</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -653,16 +653,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Шапка шарф PKBFLOW</t>
+          <t>Шапка бини</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>421 ₽</t>
+          <t>1 123 ₽</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>319 ₽</t>
+          <t>1 308 ₽</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -693,12 +693,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Шапка бини</t>
+          <t>Шапка бини Шапка</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1 305 ₽</t>
+          <t>624 ₽</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -713,12 +713,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Шапка бини WloO! шапки и снуды</t>
+          <t>снуд шарф из флиса (мужcкой, женский) черный нуар</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>988 ₽</t>
+          <t>368 ₽</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -733,12 +733,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Шапка бини</t>
+          <t>Шапка ушанка</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1 305 ₽</t>
+          <t>1 169 ₽</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -753,16 +753,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Шапка MARSTON мужская теплая с отворотом и флисовым подкладом</t>
+          <t>Шапка бини Aldini Весенняя коллекция</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>624 ₽</t>
+          <t>461 ₽</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -773,12 +773,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Шапка с помпоном Зимняя</t>
+          <t>Шапка комплект с аксессуаром</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>810 ₽</t>
+          <t>460 ₽</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -793,16 +793,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Шапка шарф</t>
+          <t>Шапка бини WARM WHIFF Зимняя коллекция</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>169 ₽</t>
+          <t>810 ₽</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -813,16 +813,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Шапка бини шапка мужская</t>
+          <t>Шапка с помпоном Star Dust</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>567 ₽</t>
+          <t>563 ₽</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -833,12 +833,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Шапка зимняя черная</t>
+          <t>Шапка MARSTON мужская теплая</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>196 ₽</t>
+          <t>502 ₽</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -853,12 +853,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Шапка с помпоном Зимняя</t>
+          <t>Шапка karoca Теплая шапка с флисовым подкладом</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>935 ₽</t>
+          <t>501 ₽</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -873,16 +873,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Шапка ушанка 1131</t>
+          <t>Шапка бини FashionVerse</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1 395 ₽</t>
+          <t>357 ₽</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -893,12 +893,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Шапка бини WARM WHIFF Зимняя коллекция</t>
+          <t>Шапка бини FashionVerse</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>808 ₽</t>
+          <t>553 ₽</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -913,16 +913,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Шапка ушанка My Strategy HAT</t>
+          <t>Шапка бини</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1 532 ₽</t>
+          <t>1 308 ₽</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
